--- a/out/MLP-mamba2_repeat_1_000007.xlsx
+++ b/out/MLP-mamba2_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.242781613595273</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.242781613595273</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.778954327415217</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.242781613595273</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6427816135952729</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002814145737043582</v>
+        <v>-0.0002558379968549125</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.24429433647459</v>
+        <v>2.949434255239926</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.493603918055085</v>
+        <v>5.903427803557751</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4864964305137913</v>
+        <v>0.4422808233376368</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.378954327415217</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.217948001837803</v>
+        <v>3.834596648527906</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6082787771029895</v>
+        <v>0.5529948813046265</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.378954327415217</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.948086498132334</v>
+        <v>4.498375938655091</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8719649049497752</v>
+        <v>0.7927155398263401</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.08408069614846</v>
+        <v>5.53112442867748</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9328297296753111</v>
+        <v>0.8480486066904452</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.077840262685238</v>
+        <v>6.434565577004671</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9886114929156514</v>
+        <v>0.8987613287251282</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.122304106057234</v>
+        <v>7.384103103526692</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4461413139277561</v>
+        <v>0.4055942717942126</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.02515504150975</v>
+        <v>7.295783451296595</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2154658630507062</v>
+        <v>0.1958828518027796</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.009595572462361</v>
+        <v>7.281638129078038</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1026636818121207</v>
+        <v>0.09333295997584183</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.99928467592231</v>
+        <v>7.272264351739246</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03041816960038723</v>
+        <v>0.02765354180644621</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.957348704034732</v>
+        <v>7.234139785081767</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02012048488135915</v>
+        <v>0.01829178669006932</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.778954327415217</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.967155856541881</v>
+        <v>7.243055612526054</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01029602612442744</v>
+        <v>0.009360284807746713</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.967614348903533</v>
+        <v>7.243471980747767</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005264876289604388</v>
+        <v>0.00478570511217331</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.967840963035662</v>
+        <v>7.243677535027578</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001975767828267875</v>
+        <v>0.001795629217978324</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.966524387256585</v>
+        <v>7.242480216228637</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001074932824231511</v>
+        <v>0.0009767571129377368</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.966696624339798</v>
+        <v>7.242636340849742</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005147533876651468</v>
+        <v>0.0004678643205822054</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.966651310639631</v>
+        <v>7.242594691590229</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003167533234012582</v>
+        <v>0.000287234669878207</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.966770010309195</v>
+        <v>7.242702060047218</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001638165418276141</v>
+        <v>0.0001483760044653323</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.966779718601377</v>
+        <v>7.242710423068776</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.692563672438457e-05</v>
+        <v>6.893289167810316e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.966769647645563</v>
+        <v>7.242700816527956</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.744500148827117e-05</v>
+        <v>4.232841597722033e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.966787575946011</v>
+        <v>7.242716788310757</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.831222555273368e-05</v>
+        <v>1.7146614275097e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.966777887090603</v>
+        <v>7.242707441886049</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.96677001004369</v>
+        <v>7.242699838903246</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.966765920231201</v>
+        <v>7.242695665731654</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.966760052788517</v>
+        <v>7.242689943452624</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.778954327415217</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.966754983433148</v>
+        <v>7.242684874097255</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.96675061845918</v>
+        <v>7.242680509123287</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.966751709705636</v>
+        <v>7.242681600369743</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.9667510200985</v>
+        <v>7.242680910762608</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.966751050410902</v>
+        <v>7.242680941075009</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.966750860958392</v>
+        <v>7.242680751622499</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.966750914005095</v>
+        <v>7.242680804669202</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.966750967051796</v>
+        <v>7.242680857715905</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.966750929161296</v>
+        <v>7.242680819825402</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.966750800333589</v>
+        <v>7.242680690997696</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.966750656349681</v>
+        <v>7.242680547013788</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.966750497209573</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.966750550256276</v>
+        <v>7.242680440920383</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.966750497209573</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.966750497209573</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.966750315335164</v>
+        <v>7.242680205999271</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.966750482053373</v>
+        <v>7.242680372717479</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.966750679083982</v>
+        <v>7.24268056974809</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.966750519943874</v>
+        <v>7.242680410607981</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.966750557834375</v>
+        <v>7.242680448498483</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.966750754864987</v>
+        <v>7.242680645529093</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.966750732130686</v>
+        <v>7.242680622794792</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.966750580568677</v>
+        <v>7.242680471232784</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.778954327415217</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.966750504787674</v>
+        <v>7.242680395451781</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.242781613595273</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.966750603302978</v>
+        <v>7.242680493967086</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.966750610881079</v>
+        <v>7.242680501545186</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.966750876114592</v>
+        <v>7.2426807667787</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.378954327415217</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.966750580568677</v>
+        <v>7.242680471232784</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.378954327415217</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.966750823067891</v>
+        <v>7.242680713731997</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.966750906426994</v>
+        <v>7.242680797091102</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.966750739708785</v>
+        <v>7.242680630372893</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.966750929161296</v>
+        <v>7.242680819825402</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.966750580568677</v>
+        <v>7.242680471232784</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.966750375959966</v>
+        <v>7.242680266624074</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.966750489631472</v>
+        <v>7.242680380295579</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.966750504787674</v>
+        <v>7.242680395451781</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.242781613595273</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.966750269866561</v>
+        <v>7.242680160530669</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.966750330491364</v>
+        <v>7.242680221155471</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.966750201663658</v>
+        <v>7.242680092327764</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.966750338069465</v>
+        <v>7.242680228733573</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.966750512365773</v>
+        <v>7.242680403029881</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.966750656349681</v>
+        <v>7.242680547013788</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.242781613595273</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.966750489631472</v>
+        <v>7.242680380295579</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.966750482053373</v>
+        <v>7.242680372717479</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.966750194085557</v>
+        <v>7.242680084749664</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.378954327415217</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.966750209241757</v>
+        <v>7.242680099905865</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6427816135952729</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.96675043658477</v>
+        <v>7.242680327248877</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.966750421428569</v>
+        <v>7.242680312092676</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.8241370729394373</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.966750527521976</v>
+        <v>7.242680418186081</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.96675025471036</v>
+        <v>7.242680145374468</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.378954327415217</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.966750353225665</v>
+        <v>7.242680243889772</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6427816135952729</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.966750504787674</v>
+        <v>7.242680395451781</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6427816135952729</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.966750519943874</v>
+        <v>7.242680410607981</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.778954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.966750497209573</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.378954327415217</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.966750580568677</v>
+        <v>7.242680471232784</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.966750679083982</v>
+        <v>7.24268056974809</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.966750512365773</v>
+        <v>7.242680403029881</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.966750497209573</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.242781613595273</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.966750466897171</v>
+        <v>7.242680357561278</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.778954327415217</v>
+        <v>1.443559541701984</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.966750451740971</v>
+        <v>7.242680342405078</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-1.424137072939437</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.966750489631472</v>
+        <v>7.242680380295579</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6427816135952729</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.966750504787674</v>
+        <v>7.242680395451781</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.242781613595273</v>
+        <v>2.043559541701984</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.966750497209573</v>
+        <v>7.242680387873681</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000007.xlsx
+++ b/out/MLP-mamba2_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.4864788207510443</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4864788207510443</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.4864788207510443</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.778954327415217</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002814145737043582</v>
+        <v>-0.0001155721882991493</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.24429433647459</v>
+        <v>1.332376641911318</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.493603918055085</v>
+        <v>2.66681289765869</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4864964305137913</v>
+        <v>0.1997957981974834</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.217948001837803</v>
+        <v>1.732239664845153</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6082787771029895</v>
+        <v>0.2498098138360472</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.948086498132334</v>
+        <v>2.032095177912365</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8719649049497752</v>
+        <v>0.3581011834354985</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.08408069614846</v>
+        <v>2.498628709682049</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9328297296753111</v>
+        <v>0.383096985610655</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.077840262685238</v>
+        <v>2.906748893500904</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9886114929156514</v>
+        <v>0.4060055879735534</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.122304106057234</v>
+        <v>3.335692853326638</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4461413139277561</v>
+        <v>0.1832227706460179</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.02515504150975</v>
+        <v>3.295795273630667</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2154658630507062</v>
+        <v>0.08848886690537108</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.009595572462361</v>
+        <v>3.289405232337381</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1026636818121207</v>
+        <v>0.04216231059913917</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.99928467592231</v>
+        <v>3.285170714202012</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03041816960038723</v>
+        <v>0.01249121969852168</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.957348704034732</v>
+        <v>3.267947111003152</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02012048488135915</v>
+        <v>0.008260772389627169</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.778954327415217</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.967155856541881</v>
+        <v>3.271972217848197</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01029602612442744</v>
+        <v>0.004225023049853238</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.967614348903533</v>
+        <v>3.272157560185896</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005264876289604388</v>
+        <v>0.002159323595539529</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.967840963035662</v>
+        <v>3.272247683468433</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001975767828267875</v>
+        <v>0.0008086512859717101</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.966524387256585</v>
+        <v>3.27170402273882</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001074932824231511</v>
+        <v>0.0004380282097878695</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.966696624339798</v>
+        <v>3.271771800119483</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005147533876651468</v>
+        <v>0.0002087823567001903</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.966651310639631</v>
+        <v>3.271750230958459</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003167533234012582</v>
+        <v>0.0001268499857362954</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.966770010309195</v>
+        <v>3.271796033160465</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001638165418276141</v>
+        <v>6.396773355152526e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.966779718601377</v>
+        <v>3.271797087504533</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.692563672438457e-05</v>
+        <v>2.896916644669604e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.966769647645563</v>
+        <v>3.271789984913097</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.744500148827117e-05</v>
+        <v>1.67454884219661e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.966787575946011</v>
+        <v>3.27179449176938</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.831222555273368e-05</v>
+        <v>4.324890221093473e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.966777887090603</v>
+        <v>3.271787548024312</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>-8.825233700581938e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.96677001004369</v>
+        <v>3.271781315362063</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.966765920231201</v>
+        <v>3.271776729452531</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.966760052788517</v>
+        <v>3.271771296321063</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.778954327415217</v>
+        <v>0.6948861808537512</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.966754983433148</v>
+        <v>3.271766249699995</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.96675061845918</v>
+        <v>3.271766567980211</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.966751709705636</v>
+        <v>3.271767659226668</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.9667510200985</v>
+        <v>3.271766969619532</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.966751050410902</v>
+        <v>3.271766999931934</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.966750860958392</v>
+        <v>3.271766810479424</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.966750914005095</v>
+        <v>3.271766863526127</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.966750967051796</v>
+        <v>3.27176691657283</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.966750929161296</v>
+        <v>3.271766878682327</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.966750800333589</v>
+        <v>3.271766749854621</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.966750656349681</v>
+        <v>3.271766605870714</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.966750497209573</v>
+        <v>3.271766446730605</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.966750550256276</v>
+        <v>3.271766499777308</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.966750497209573</v>
+        <v>3.271766446730605</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.966750497209573</v>
+        <v>3.271766446730605</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.966750315335164</v>
+        <v>3.271766264856196</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.966750482053373</v>
+        <v>3.271766431574404</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.966750679083982</v>
+        <v>3.271766628605015</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.966750519943874</v>
+        <v>3.271766469464906</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.966750557834375</v>
+        <v>3.271766507355408</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.966750754864987</v>
+        <v>3.271766704386018</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.966750732130686</v>
+        <v>3.271766681651717</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.966750580568677</v>
+        <v>3.271766530089709</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.778954327415217</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.966750504787674</v>
+        <v>3.271766454308705</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.6948861808537512</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.966750603302978</v>
+        <v>3.271766552824011</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.378954327415217</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.966750610881079</v>
+        <v>3.271766560402111</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.966750876114592</v>
+        <v>3.271766825635625</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.966750580568677</v>
+        <v>3.271766530089709</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.966750823067891</v>
+        <v>3.271766772588922</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.966750906426994</v>
+        <v>3.271766855948026</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.966750739708785</v>
+        <v>3.271766689229818</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.966750929161296</v>
+        <v>3.271766878682327</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.966750580568677</v>
+        <v>3.271766530089709</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.966750375959966</v>
+        <v>3.271766325480999</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.966750489631472</v>
+        <v>3.271766439152505</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.966750504787674</v>
+        <v>3.271766454308705</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.966750269866561</v>
+        <v>3.271766219387594</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.966750330491364</v>
+        <v>3.271766280012396</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.966750201663658</v>
+        <v>3.271766151184689</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.966750338069465</v>
+        <v>3.271766287590497</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.966750512365773</v>
+        <v>3.271766461886806</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.4864788207510443</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.966750656349681</v>
+        <v>3.271766605870714</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.966750489631472</v>
+        <v>3.271766439152505</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.966750482053373</v>
+        <v>3.271766431574404</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.966750194085557</v>
+        <v>3.271766143606589</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.378954327415217</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.966750209241757</v>
+        <v>3.27176615876279</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.96675043658477</v>
+        <v>3.271766386105802</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.966750421428569</v>
+        <v>3.271766370949601</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.966750527521976</v>
+        <v>3.271766477043006</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.96675025471036</v>
+        <v>3.271766204231393</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.966750353225665</v>
+        <v>3.271766302746697</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.966750504787674</v>
+        <v>3.271766454308705</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.966750519943874</v>
+        <v>3.271766469464906</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.778954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.966750497209573</v>
+        <v>3.271766446730605</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.966750580568677</v>
+        <v>3.271766530089709</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.2042036800513535</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.966750679083982</v>
+        <v>3.271766628605015</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.966750512365773</v>
+        <v>3.271766461886806</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.966750497209573</v>
+        <v>3.271766446730605</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.966750466897171</v>
+        <v>3.271766416418203</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.778954327415217</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.966750451740971</v>
+        <v>3.271766401262003</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6427816135952729</v>
+        <v>0.004203680051353437</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.966750489631472</v>
+        <v>3.271766439152505</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6427816135952729</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.966750504787674</v>
+        <v>3.271766454308705</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510444</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.966750497209573</v>
+        <v>3.271766446730605</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000007.xlsx
+++ b/out/MLP-mamba2_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.263219952583313</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4808781147003174</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3842908143997192</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.2926008701324463</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.3748037815093994</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.3697041273117065</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3024588525295258</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.2187000960111618</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4527034759521484</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3045186102390289</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3160178363323212</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6864788207510444</v>
+        <v>0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.2953006029129028</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.2042036800513535</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5438277125358582</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.2042036800513535</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.2086328715085983</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.2042036800513535</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.2312541604042053</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4864788207510443</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.2710493206977844</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4864788207510443</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4492082297801971</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6864788207510444</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.2666753530502319</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6864788207510444</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.3382083773612976</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.004203680051353437</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.6437407732009888</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.7451575398445129</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.585568681656149</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.8427836894989014</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3495737612247467</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4350259900093079</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4864788207510443</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4165582358837128</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3407964706420898</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3010766208171844</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.7790889143943787</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3813402354717255</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4394303560256958</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3974650204181671</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.2012099176645279</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6864788207510444</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4896087050437927</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.004203680051353437</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.531663715839386</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.8395769596099854</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.585568681656149</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.9566540122032166</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4946516156196594</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.7837784290313721</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001155721882991493</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.332376641911318</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.3092561662197113</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.66681289765869</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1997957981974834</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5988120436668396</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.8948861808537513</v>
+        <v>-0.16</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.732239664845153</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2498098138360472</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.6323536038398743</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.032095177912365</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3581011834354985</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.915979266166687</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.585568681656149</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.498628709682049</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.383096985610655</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9429607391357422</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.585568681656149</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.906748893500904</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4060055879735534</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.9155295491218567</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.585568681656149</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>3.335692853326638</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1832227706460179</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.7771340012550354</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.295795273630667</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.08848886690537108</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.05961787328124046</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.289405232337381</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04216231059913917</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.2594572305679321</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.285170714202012</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01249121969852168</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.244393453001976</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.267947111003152</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008260772389627169</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5195122957229614</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.271972217848197</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.004225023049853238</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.1109989136457443</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.272157560185896</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002159323595539529</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3618170320987701</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.272247683468433</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008086512859717101</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4211788773536682</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.27170402273882</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004380282097878695</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4328624606132507</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.271771800119483</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002087823567001903</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.6454742550849915</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.271750230958459</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001268499857362954</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5727629065513611</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.271796033160465</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.396773355152526e-05</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.237350270152092</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.271797087504533</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.896916644669604e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.9865955710411072</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.271789984913097</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.67454884219661e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.246639296412468</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2042036800513535</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.27179449176938</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>4.324890221093473e-06</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.1239645704627037</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.271787548024312</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-8.825233700581938e-07</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3335356116294861</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.271781315362063</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.1698439121246338</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.271776729452531</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3070683777332306</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.271771296321063</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.8788259625434875</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.6948861808537512</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.271766249699995</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9766031503677368</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.585568681656149</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.271766567980211</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.9720805287361145</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.271767659226668</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.07630546391010284</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.271766969619532</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.04834954813122749</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.271766999931934</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.08861036598682404</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.271766810479424</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.2207496762275696</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.271766863526127</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.1196350231766701</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.27176691657283</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.213473379611969</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.271766878682327</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2066394090652466</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.271766749854621</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.257294088602066</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.271766605870714</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4007715284824371</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6864788207510444</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.271766446730605</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.369535505771637</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6864788207510444</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.271766499777308</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3741579055786133</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6864788207510444</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.271766446730605</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.2051188200712204</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.271766446730605</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.7997395992279053</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.271766264856196</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.7726634740829468</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.271766431574404</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.1444684267044067</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.271766628605015</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4196373522281647</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.271766469464906</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.7328491806983948</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.271766507355408</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.6316657066345215</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.271766704386018</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.2161202281713486</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2042036800513535</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.271766681651717</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3139537274837494</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2042036800513535</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.271766530089709</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.5019976496696472</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.271766454308705</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.446659654378891</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6948861808537512</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.271766552824011</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.7587242126464844</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.271766560402111</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.3396385312080383</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.271766825635625</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5922517776489258</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.271766530089709</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.719947874546051</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.271766772588922</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.1149778813123703</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.271766855948026</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.9345963597297668</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2042036800513535</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.271766689229818</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.09041864424943924</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.271766878682327</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.2299671620130539</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.271766530089709</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2474014461040497</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.271766325480999</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4210030138492584</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.271766439152505</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.1659585982561111</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.271766454308705</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4634339213371277</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6864788207510444</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.271766219387594</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.1867853850126266</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.004203680051353437</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.271766280012396</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.6156017184257507</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.271766151184689</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.9185160994529724</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.271766287590497</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4796946346759796</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.271766461886806</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2427931129932404</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4864788207510443</v>
+        <v>0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.271766605870714</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4384653568267822</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.271766439152505</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.0883210152387619</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.271766431574404</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3631806969642639</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.271766143606589</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.7656967639923096</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.27176615876279</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3673700988292694</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.8948861808537513</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.271766386105802</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.7296624183654785</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.271766370949601</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.0858880952000618</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.271766477043006</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4488376677036285</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.271766204231393</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.6897165775299072</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.271766302746697</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4757963716983795</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.2042036800513535</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.271766454308705</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4970628619194031</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.004203680051353437</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.271766469464906</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.5178390741348267</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.271766446730605</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.579780638217926</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.271766530089709</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3024420440196991</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2042036800513535</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.271766628605015</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2451495826244354</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.271766461886806</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4186456799507141</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6864788207510444</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.271766446730605</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3587109446525574</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.271766416418203</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.5161558389663696</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.271766401262003</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4383626580238342</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.004203680051353437</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.271766439152505</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.463178426027298</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6864788207510444</v>
+        <v>0.6500000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.271766454308705</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4331038892269135</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6864788207510444</v>
+        <v>0.8600000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.271766446730605</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000007.xlsx
+++ b/out/MLP-mamba2_repeat_1_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.263219952583313</v>
+        <v>0.263219803571701</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.4399999999999999</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.4808781147003174</v>
+        <v>0.4808779954910278</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.58</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.3842908143997192</v>
+        <v>0.3842906951904297</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.2926008701324463</v>
+        <v>0.2926009297370911</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.3697041273117065</v>
+        <v>0.3697039186954498</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.3024588525295258</v>
+        <v>0.3024587035179138</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.2187000960111618</v>
+        <v>0.2186999171972275</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4527034759521484</v>
+        <v>0.4527031779289246</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.3045186102390289</v>
+        <v>0.3045184314250946</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.1199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.3160178363323212</v>
+        <v>0.3160175383090973</v>
       </c>
       <c r="JB12" t="n">
         <v>0.16</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.2953006029129028</v>
+        <v>0.2953003942966461</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.1199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.5438277125358582</v>
+        <v>0.5438274741172791</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.2086328715085983</v>
+        <v>0.2086326330900192</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.2312541604042053</v>
+        <v>0.2312539666891098</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.2710493206977844</v>
+        <v>0.2710490226745605</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.1199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4492082297801971</v>
+        <v>0.4492079019546509</v>
       </c>
       <c r="JB18" t="n">
         <v>0.02000000000000007</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.2666753530502319</v>
+        <v>0.2666750848293304</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.3382083773612976</v>
+        <v>0.3382079601287842</v>
       </c>
       <c r="JB20" t="n">
         <v>0.5799999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.6437407732009888</v>
+        <v>0.6437403559684753</v>
       </c>
       <c r="JB21" t="n">
         <v>0.5799999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.7451575398445129</v>
+        <v>0.7451573014259338</v>
       </c>
       <c r="JB22" t="n">
         <v>0.5799999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3495737612247467</v>
+        <v>0.3495734632015228</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.4350259900093079</v>
+        <v>0.4350257217884064</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.4165582358837128</v>
+        <v>0.4165579378604889</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.5799999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.3407964706420898</v>
+        <v>0.3407962322235107</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.3010766208171844</v>
+        <v>0.3010763823986053</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.7790889143943787</v>
+        <v>0.7790887355804443</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3813402354717255</v>
+        <v>0.3813400864601135</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.4394303560256958</v>
+        <v>0.4394301474094391</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.3974650204181671</v>
+        <v>0.3974648118019104</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.2012099176645279</v>
+        <v>0.2012097835540771</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4896087050437927</v>
+        <v>0.4896084666252136</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.531663715839386</v>
+        <v>0.5316635370254517</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.8395769596099854</v>
+        <v>0.8395770192146301</v>
       </c>
       <c r="JB36" t="n">
         <v>0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.4946516156196594</v>
+        <v>0.4946515560150146</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.7837784290313721</v>
+        <v>0.7837783694267273</v>
       </c>
       <c r="JB39" t="n">
         <v>0.5799999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.7771340012550354</v>
+        <v>0.7771340608596802</v>
       </c>
       <c r="JB46" t="n">
         <v>0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.05961787328124046</v>
+        <v>0.05961786210536957</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.2594572305679321</v>
+        <v>0.2594572007656097</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.244393453001976</v>
+        <v>0.2443935126066208</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.1239645704627037</v>
+        <v>0.1239645853638649</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.3335356116294861</v>
+        <v>0.3335356414318085</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.1698439121246338</v>
+        <v>0.1698438972234726</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.3070683777332306</v>
+        <v>0.307068407535553</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.9720805287361145</v>
+        <v>0.972080409526825</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.07630546391010284</v>
+        <v>0.07630543410778046</v>
       </c>
       <c r="JB67" t="n">
         <v>0.16</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.04834954813122749</v>
+        <v>0.04834950715303421</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.08861036598682404</v>
+        <v>0.08861035108566284</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.2207496762275696</v>
+        <v>0.220749631524086</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.1196350231766701</v>
+        <v>0.1196349859237671</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.2066394090652466</v>
+        <v>0.2066394984722137</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.4007715284824371</v>
+        <v>0.40077143907547</v>
       </c>
       <c r="JB75" t="n">
         <v>0.1600000000000001</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.369535505771637</v>
+        <v>0.3695354759693146</v>
       </c>
       <c r="JB76" t="n">
         <v>0.16</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3741579055786133</v>
+        <v>0.3741578161716461</v>
       </c>
       <c r="JB77" t="n">
         <v>0.4399999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.2051188200712204</v>
+        <v>0.205118790268898</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.4196373522281647</v>
+        <v>0.4196372926235199</v>
       </c>
       <c r="JB82" t="n">
         <v>0.5799999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.6316657066345215</v>
+        <v>0.6316657662391663</v>
       </c>
       <c r="JB84" t="n">
         <v>0.3</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.2161202281713486</v>
+        <v>0.2161201387643814</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.3</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.3139537274837494</v>
+        <v>0.3139536380767822</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.5019976496696472</v>
+        <v>0.5019975304603577</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.446659654378891</v>
+        <v>0.4466596245765686</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.3396385312080383</v>
+        <v>0.3396386802196503</v>
       </c>
       <c r="JB90" t="n">
         <v>0.5799999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.5922517776489258</v>
+        <v>0.5922520160675049</v>
       </c>
       <c r="JB91" t="n">
         <v>0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.719947874546051</v>
+        <v>0.7199479341506958</v>
       </c>
       <c r="JB92" t="n">
         <v>0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.2299671620130539</v>
+        <v>0.2299674153327942</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.2474014461040497</v>
+        <v>0.2474015057086945</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.1867853850126266</v>
+        <v>0.1867853403091431</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.6156017184257507</v>
+        <v>0.6156021952629089</v>
       </c>
       <c r="JB102" t="n">
         <v>0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.2427931129932404</v>
+        <v>0.2427930384874344</v>
       </c>
       <c r="JB105" t="n">
         <v>0.16</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.4384653568267822</v>
+        <v>0.4384653270244598</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.0883210152387619</v>
+        <v>0.08832097798585892</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.3631806969642639</v>
+        <v>0.3631811439990997</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3673700988292694</v>
+        <v>0.3673701286315918</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.4399999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.0858880952000618</v>
+        <v>0.08588824421167374</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.4488376677036285</v>
+        <v>0.448838084936142</v>
       </c>
       <c r="JB113" t="n">
         <v>0.5799999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.6897165775299072</v>
+        <v>0.6897165179252625</v>
       </c>
       <c r="JB114" t="n">
         <v>0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4970628619194031</v>
+        <v>0.4970628023147583</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.3024420440196991</v>
+        <v>0.3024425506591797</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.2451495826244354</v>
+        <v>0.24515001475811</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.5799999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.4186456799507141</v>
+        <v>0.4186461865901947</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.3587109446525574</v>
+        <v>0.358710765838623</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.4383626580238342</v>
+        <v>0.4383632242679596</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.16</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.463178426027298</v>
+        <v>0.4631783366203308</v>
       </c>
       <c r="JB125" t="n">
         <v>0.6500000000000001</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.4331038892269135</v>
+        <v>0.4331039190292358</v>
       </c>
       <c r="JB126" t="n">
         <v>0.8600000000000003</v>
